--- a/examples/example01/HFP_robin.xlsx
+++ b/examples/example01/HFP_robin.xlsx
@@ -1123,7 +1123,7 @@
         <v>300000</v>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
